--- a/Lab 2/PCB2_Lab2/Generate Files/BOM/PCB2_Lab2.xlsx
+++ b/Lab 2/PCB2_Lab2/Generate Files/BOM/PCB2_Lab2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Session 5\Devlo-session-5\Lab 2\PCB2_Lab2\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACE7A620-7DB3-49A3-AAD5-39DCD3DA632D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A750EC3D-6401-44A6-90A1-82E16090EBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3225D40C-D1E0-429D-86A8-109520C7681B}"/>
+    <workbookView xWindow="-15870" yWindow="-3615" windowWidth="15990" windowHeight="24720" xr2:uid="{102B0E0F-D1BF-4741-8696-AEFF3A136532}"/>
   </bookViews>
   <sheets>
     <sheet name="PCB2_Lab2" sheetId="1" r:id="rId1"/>
@@ -671,7 +671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC9BC3D-AD9F-4560-8276-2B561A022A4F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC20E4B-9435-40A4-9575-BDD026938B99}">
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>

--- a/Lab 2/PCB2_Lab2/Generate Files/BOM/PCB2_Lab2.xlsx
+++ b/Lab 2/PCB2_Lab2/Generate Files/BOM/PCB2_Lab2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Session 5\Devlo-session-5\Lab 2\PCB2_Lab2\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A750EC3D-6401-44A6-90A1-82E16090EBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E3BF683-5795-41EF-95BA-8690CA51A5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15870" yWindow="-3615" windowWidth="15990" windowHeight="24720" xr2:uid="{102B0E0F-D1BF-4741-8696-AEFF3A136532}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{03033314-7FB2-4FF1-A0ED-926AD6773EE2}"/>
   </bookViews>
   <sheets>
     <sheet name="PCB2_Lab2" sheetId="1" r:id="rId1"/>
@@ -671,7 +671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC20E4B-9435-40A4-9575-BDD026938B99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DECB0F20-FBE7-4E95-BCDB-A1174D58B3A6}">
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
